--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487417_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487417_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7098</v>
+        <v>5.3004</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6448</v>
+        <v>4.2355</v>
       </c>
       <c r="F2" t="n">
         <v>1.065</v>
@@ -610,10 +610,10 @@
         <v>0.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8428</v>
+        <v>0.4335</v>
       </c>
       <c r="T2" t="n">
-        <v>0.117</v>
+        <v>-0.2923</v>
       </c>
       <c r="U2" t="n">
         <v>0.7258</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1075</v>
+        <v>1.8111</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8951</v>
+        <v>2.5452</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7876</v>
+        <v>-0.7341</v>
       </c>
       <c r="G3" t="n">
         <v>0.7631</v>
@@ -688,13 +688,13 @@
         <v>0.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0115</v>
+        <v>-0.285</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3852</v>
+        <v>0.0353</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3737</v>
+        <v>-0.3202</v>
       </c>
       <c r="V3" t="n">
         <v>0.9412</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0789</v>
+        <v>0.2295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2898</v>
+        <v>0.7585</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3687</v>
+        <v>-0.5291</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0997</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6462</v>
+        <v>-0.3379</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0692</v>
+        <v>-0.6005</v>
       </c>
       <c r="U4" t="n">
-        <v>0.423</v>
+        <v>0.2626</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SANTORUM OTERO</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8357</v>
+        <v>-0.2293</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7439</v>
+        <v>2.42</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0919</v>
+        <v>-2.6493</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1581</v>
+        <v>2.5462</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0269</v>
+        <v>-1.298</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313</v>
+        <v>3.8443</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0408</v>
+        <v>3.3275</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0408</v>
+        <v>-0.2127</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.5402</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.199</v>
+        <v>-0.7813</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0677</v>
+        <v>-1.0853</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1313</v>
+        <v>0.304</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0117</v>
+        <v>-0.3423</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>0.0717</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1071</v>
+        <v>-0.414</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6659</v>
+        <v>-2.4332</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>P. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.985</v>
+        <v>-0.9159</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1989</v>
+        <v>-0.7439</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1839</v>
+        <v>-0.1721</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5462</v>
+        <v>-0.1581</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.298</v>
+        <v>-0.0269</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8443</v>
+        <v>-0.1313</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3275</v>
+        <v>0.0408</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2127</v>
+        <v>0.0408</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5402</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7813</v>
+        <v>-0.199</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0853</v>
+        <v>-0.0677</v>
       </c>
       <c r="O6" t="n">
-        <v>0.304</v>
+        <v>-0.1313</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.098</v>
+        <v>-0.0919</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.1188</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9487</v>
+        <v>0.0269</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4332</v>
+        <v>-0.6659</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5469</v>
+        <v>-2.5467</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3898</v>
+        <v>-1.4162</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1572</v>
+        <v>-1.1304</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7049</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5874</v>
+        <v>-0.5871</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0288</v>
+        <v>0.0023</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6162</v>
+        <v>-0.5895</v>
       </c>
       <c r="V7" t="n">
         <v>0.3329</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7438</v>
+        <v>-2.5775</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0944</v>
+        <v>-2.035</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6493</v>
+        <v>-0.5424</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9754</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.985</v>
+        <v>-0.8187</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5346</v>
+        <v>-0.4752</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4504</v>
+        <v>-0.3435</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4893</v>
+        <v>-4.8646</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1262</v>
+        <v>-4.3144</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3632</v>
+        <v>-0.5503</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2761</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7245</v>
+        <v>0.3492</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0612</v>
+        <v>-0.2494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7857</v>
+        <v>0.5986</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5147</v>
+        <v>-5.111</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6687</v>
+        <v>-4.3452</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.846</v>
+        <v>-0.7658</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9727</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3912</v>
+        <v>0.0125</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6246</v>
+        <v>-0.3011</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2334</v>
+        <v>0.3136</v>
       </c>
       <c r="V10" t="n">
         <v>2.7662</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.608</v>
+        <v>-6.4775</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6226</v>
+        <v>-5.3585</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-1.119</v>
       </c>
       <c r="G11" t="n">
         <v>-3.095</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3379</v>
+        <v>-0.2075</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.891</v>
+        <v>-0.627</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5531</v>
+        <v>0.4195</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.306699999999999</v>
+        <v>-9.0191</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.2224</v>
+        <v>-8.6942</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0843</v>
+        <v>-0.3249</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9085</v>
@@ -1390,13 +1390,13 @@
         <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.109</v>
+        <v>-0.8215</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1286</v>
+        <v>-0.6005</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0196</v>
+        <v>-0.221</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2178</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.2917</v>
+        <v>-24.4006</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.8394</v>
+        <v>-16.9482</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.452500000000001</v>
+        <v>-7.4524</v>
       </c>
       <c r="G13" t="n">
         <v>-7.405800000000001</v>
@@ -1438,7 +1438,7 @@
         <v>1.3853</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.791199999999998</v>
+        <v>-8.7912</v>
       </c>
       <c r="J13" t="n">
         <v>1.469400000000001</v>
@@ -1468,16 +1468,16 @@
         <v>5.8753</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5876</v>
+        <v>-2.6967</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.0464</v>
+        <v>-3.1555</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4587000000000001</v>
+        <v>0.4588</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3905000000000003</v>
+        <v>0.3905000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.302</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3391</v>
+        <v>8.6774</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2495</v>
+        <v>6.4541</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0896</v>
+        <v>2.2233</v>
       </c>
       <c r="G14" t="n">
         <v>5.6463</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6414</v>
+        <v>-0.303</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5652</v>
+        <v>-0.3605</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0762</v>
+        <v>0.0575</v>
       </c>
       <c r="V14" t="n">
         <v>1.7673</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7195</v>
+        <v>6.3891</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6938</v>
+        <v>3.3635</v>
       </c>
       <c r="F15" t="n">
         <v>3.0257</v>
@@ -1624,10 +1624,10 @@
         <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3372</v>
+        <v>1.0069</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0096</v>
+        <v>0.6793</v>
       </c>
       <c r="U15" t="n">
         <v>0.3276</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8851</v>
+        <v>4.5038</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9468</v>
+        <v>0.3497</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9382</v>
+        <v>4.1541</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4113</v>
+        <v>1.6459</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5533</v>
+        <v>1.2722</v>
       </c>
       <c r="I16" t="n">
-        <v>0.142</v>
+        <v>0.3737</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8435</v>
+        <v>0.6773</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2825</v>
+        <v>1.9513</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.274</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4322</v>
+        <v>0.9686</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2708</v>
+        <v>-0.6791</v>
       </c>
       <c r="O16" t="n">
-        <v>0.703</v>
+        <v>1.6477</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8252</v>
+        <v>0.7036</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08169999999999999</v>
+        <v>-0.3276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7433999999999999</v>
+        <v>1.0312</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5489</v>
+        <v>4.4131</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0596</v>
+        <v>1.7422</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6086</v>
+        <v>2.6709</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6459</v>
+        <v>-0.4113</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2722</v>
+        <v>-0.5533</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3737</v>
+        <v>0.142</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6773</v>
+        <v>-0.8435</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9513</v>
+        <v>-0.2825</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.274</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9686</v>
+        <v>0.4322</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6791</v>
+        <v>-0.2708</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6477</v>
+        <v>0.703</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7486</v>
+        <v>0.3532</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7369</v>
+        <v>-0.1229</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4856</v>
+        <v>0.4761</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9543</v>
+        <v>2.5065</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.164</v>
+        <v>0.0406</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1183</v>
+        <v>2.4658</v>
       </c>
       <c r="G18" t="n">
         <v>2.533</v>
@@ -1858,13 +1858,13 @@
         <v>2.3502</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8552</v>
+        <v>-0.303</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3276</v>
+        <v>-0.1229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5276</v>
+        <v>-0.1801</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1152</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7481</v>
+        <v>1.5732</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8274</v>
+        <v>0.9446</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0793</v>
+        <v>0.6286</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3447</v>
+        <v>0.9873</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2787</v>
+        <v>-0.6393</v>
       </c>
       <c r="I19" t="n">
-        <v>0.066</v>
+        <v>1.6266</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4134</v>
+        <v>1.2581</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6859</v>
+        <v>0.0408</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7275</v>
+        <v>1.2173</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0687</v>
+        <v>-0.2708</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4073</v>
+        <v>-0.6802</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6615</v>
+        <v>0.4093</v>
       </c>
       <c r="P19" t="n">
         <v>0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7204</v>
+        <v>-0.1975</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3933</v>
+        <v>-0.3135</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3271</v>
+        <v>0.116</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4976</v>
+        <v>1.4841</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8423</v>
+        <v>1.043</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6553</v>
+        <v>0.441</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9873</v>
+        <v>1.0346</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6393</v>
+        <v>-0.4556</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6266</v>
+        <v>1.4902</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2581</v>
+        <v>1.2377</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0408</v>
+        <v>0.0204</v>
       </c>
       <c r="L20" t="n">
         <v>1.2173</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2708</v>
+        <v>-0.2031</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6802</v>
+        <v>-0.476</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4093</v>
+        <v>0.2729</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2731</v>
+        <v>0.0578</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4158</v>
+        <v>-0.1947</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1427</v>
+        <v>0.2525</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4085</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9407</v>
+        <v>2.0087</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4678</v>
+        <v>-1.1595</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0346</v>
+        <v>1.3447</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4556</v>
+        <v>1.2787</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4902</v>
+        <v>0.066</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2377</v>
+        <v>2.4134</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0204</v>
+        <v>1.6859</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2173</v>
+        <v>0.7275</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2031</v>
+        <v>-1.0687</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.476</v>
+        <v>-0.4073</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2729</v>
+        <v>-0.6615</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0178</v>
+        <v>0.8215</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.297</v>
+        <v>0.5746</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2792</v>
+        <v>0.2469</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0616</v>
+        <v>-0.4919</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7761</v>
+        <v>-2.3667</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7144</v>
+        <v>1.8748</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2632</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0058</v>
+        <v>0.5755</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2441</v>
+        <v>0.1653</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2498</v>
+        <v>0.4102</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2015</v>
+        <v>-1.1839</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0473</v>
+        <v>0.252</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2488</v>
+        <v>-1.4359</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5667</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8192</v>
+        <v>0.8368</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1141</v>
+        <v>0.0906</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9333</v>
+        <v>0.7462</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4479</v>
+        <v>-1.6968</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1736</v>
+        <v>-1.5829</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2743</v>
+        <v>-0.1139</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4045</v>
@@ -2326,13 +2326,13 @@
         <v>0.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0007</v>
+        <v>-0.2497</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0288</v>
+        <v>-0.3805</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0295</v>
+        <v>0.1309</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8260999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0984</v>
+        <v>-1.7322</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7055</v>
+        <v>-3.5798</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6071</v>
+        <v>1.8476</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3093</v>
@@ -2404,13 +2404,13 @@
         <v>2.546</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0806</v>
+        <v>0.2857</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2716</v>
+        <v>-0.1459</v>
       </c>
       <c r="U25" t="n">
-        <v>0.191</v>
+        <v>0.4316</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2754</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>25.29170000000001</v>
+        <v>25.2917</v>
       </c>
       <c r="E26" t="n">
         <v>8.669</v>
       </c>
       <c r="F26" t="n">
-        <v>16.6226</v>
+        <v>16.6225</v>
       </c>
       <c r="G26" t="n">
         <v>7.406000000000001</v>
@@ -2482,13 +2482,13 @@
         <v>20.5639</v>
       </c>
       <c r="S26" t="n">
-        <v>3.587600000000001</v>
+        <v>3.5878</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4588999999999999</v>
+        <v>-0.4587</v>
       </c>
       <c r="U26" t="n">
-        <v>4.0464</v>
+        <v>4.0466</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3905999999999994</v>
